--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4953FE5B-5ADB-4EA3-A484-7161348790A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898BBA13-6A69-4233-B716-3061FCC70632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="case_matrix" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">case_matrix!$A$1:$T$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">case_matrix!$A$1:$W$8</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="62">
   <si>
     <t>case_id</t>
   </si>
@@ -34,6 +34,9 @@
     <t>use_for_model</t>
   </si>
   <si>
+    <t>spacecraft_model</t>
+  </si>
+  <si>
     <t>orbit_case</t>
   </si>
   <si>
@@ -58,33 +61,33 @@
     <t>stt_heat_w</t>
   </si>
   <si>
+    <t>prop_heat_w</t>
+  </si>
+  <si>
     <t>pcdu_heat_w</t>
   </si>
   <si>
+    <t>lct_location</t>
+  </si>
+  <si>
     <t>stt_location</t>
   </si>
   <si>
-    <t>lct_location</t>
+    <t>pcdu_location</t>
+  </si>
+  <si>
+    <t>prop_location</t>
   </si>
   <si>
     <t>constraint_set</t>
   </si>
   <si>
-    <t>td_output_path</t>
-  </si>
-  <si>
-    <t>femap_model_path</t>
+    <t>td_temperature_path</t>
   </si>
   <si>
     <t>femap_result_path</t>
   </si>
   <si>
-    <t>femap_loadset_start</t>
-  </si>
-  <si>
-    <t>femap_loadset_end</t>
-  </si>
-  <si>
     <t>python_result_path</t>
   </si>
   <si>
@@ -100,6 +103,9 @@
     <t>exclude</t>
   </si>
   <si>
+    <t>baseline_bus</t>
+  </si>
+  <si>
     <t>leo_3orbit_nominal</t>
   </si>
   <si>
@@ -109,21 +115,15 @@
     <t>acquisition</t>
   </si>
   <si>
+    <t>MZ_center</t>
+  </si>
+  <si>
     <t>PZ_center</t>
   </si>
   <si>
-    <t>MZ_center</t>
-  </si>
-  <si>
     <t>stt_near_321</t>
   </si>
   <si>
-    <t>data/td_raw/TD001_lct_heat_beta30_acq/output_all_time.dat</t>
-  </si>
-  <si>
-    <t>data/femap_raw/TD001_lct_heat_beta30_acq/model.modfem</t>
-  </si>
-  <si>
     <t>data/femap_raw/TD001_lct_heat_beta30_acq/translation_rotation.xlsx</t>
   </si>
   <si>
@@ -136,92 +136,88 @@
     <t>01_LTAN06_800km_1213COLD_MZ_ZERO_HEAT</t>
   </si>
   <si>
+    <t>check</t>
+  </si>
+  <si>
+    <t>LTAN06_800km_1213COLD</t>
+  </si>
+  <si>
+    <t>ZERO_HEAT</t>
+  </si>
+  <si>
+    <t>MY_PZside</t>
+  </si>
+  <si>
+    <t>PY_MZside</t>
+  </si>
+  <si>
     <t>02_LTAN06_800km_1213COLD_MZ_ALL_HEAT</t>
   </si>
   <si>
+    <t>ALL_HEAT</t>
+  </si>
+  <si>
     <t>03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5</t>
   </si>
   <si>
+    <t>4..thermal_def_fix_mini_close_STT_all_time</t>
+  </si>
+  <si>
     <t>04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
   </si>
   <si>
+    <t>LTAN06_800km_1213COLD_MY_SUN</t>
+  </si>
+  <si>
+    <t>MY</t>
+  </si>
+  <si>
     <t>05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
   </si>
   <si>
+    <t>LTAN06_800km_1213COLD_PX_SUN</t>
+  </si>
+  <si>
+    <t>PX</t>
+  </si>
+  <si>
     <t>06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
   </si>
   <si>
-    <t>check</t>
+    <t>STTLCT_HEAT</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\Femap\research_model\03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\Femap\research_model\04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>sensitivity</t>
+    <t>C:\Users\Hide\Femap\research_model\05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\Femap\research_model\06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\repository\thermal-deformation-optcomm\results\femap_deformation\260702_1930_translation_rotation</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\repository\thermal-deformation-optcomm\results\femap_deformation\260702_1827_translation_rotation</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>exclude</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>LTAN06_800km_1213COLD</t>
-  </si>
-  <si>
-    <t>LTAN06_800km_1213COLD_MY_SUN</t>
-  </si>
-  <si>
-    <t>LTAN06_800km_1213COLD_PX_SUN</t>
-  </si>
-  <si>
-    <t>MZ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MY</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>PX</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>prop_heat_w</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ZERO_HEAT</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ALL_HEAT</t>
-  </si>
-  <si>
-    <t>STTLCT_HEAT</t>
-  </si>
-  <si>
-    <t>pcdu_location</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>prop_location</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>PY_MZside</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MY_PZside</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>4..thermal_def_fix_mini_close_STT_all_time</t>
+    <t>C:\Users\Hide\repository\thermal-deformation-optcomm\results\femap_deformation\260702_1103_translation_rotation</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\repository\thermal-deformation-optcomm\results\femap_deformation\260702_1023_translation_rotation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,8 +239,17 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,6 +267,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -275,12 +292,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -583,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="47.625" customWidth="1"/>
@@ -591,23 +612,24 @@
     <col min="3" max="3" width="17.75" customWidth="1"/>
     <col min="4" max="4" width="30.5" customWidth="1"/>
     <col min="5" max="5" width="18.5" customWidth="1"/>
-    <col min="6" max="6" width="21.875" customWidth="1"/>
+    <col min="6" max="6" width="19.25" customWidth="1"/>
     <col min="7" max="7" width="14.875" customWidth="1"/>
     <col min="8" max="8" width="21.625" customWidth="1"/>
     <col min="9" max="9" width="17.75" customWidth="1"/>
-    <col min="10" max="10" width="14.625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="14.375" customWidth="1"/>
     <col min="12" max="12" width="15.625" customWidth="1"/>
     <col min="13" max="13" width="15.875" customWidth="1"/>
     <col min="14" max="17" width="16.375" customWidth="1"/>
     <col min="18" max="18" width="35.625" customWidth="1"/>
-    <col min="19" max="20" width="42" customWidth="1"/>
-    <col min="21" max="21" width="18.5" customWidth="1"/>
-    <col min="22" max="22" width="21.5" customWidth="1"/>
-    <col min="24" max="24" width="23" customWidth="1"/>
+    <col min="19" max="19" width="42" customWidth="1"/>
+    <col min="20" max="20" width="30.75" customWidth="1"/>
+    <col min="21" max="21" width="21.5" customWidth="1"/>
+    <col min="22" max="22" width="24.5" customWidth="1"/>
+    <col min="23" max="23" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -617,7 +639,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -642,454 +664,481 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="2">
+        <v>30</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="2">
+        <v>16200</v>
+      </c>
+      <c r="I2" s="2">
+        <v>600</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="2">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2">
+        <v>2</v>
+      </c>
+      <c r="N2" s="2">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="O2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="2">
-        <v>16200</v>
-      </c>
-      <c r="H2" s="2">
-        <v>600</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="2">
-        <v>8</v>
-      </c>
-      <c r="K2" s="2">
-        <v>2</v>
-      </c>
-      <c r="M2" s="2">
-        <v>12</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="P2" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" s="2" t="s">
         <v>32</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V2" s="2">
-        <v>2</v>
-      </c>
-      <c r="W2" s="2">
-        <v>32</v>
-      </c>
-      <c r="X2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
+    <row r="3" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="4">
+        <v>-58.26</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="4">
+        <v>18157.3</v>
+      </c>
+      <c r="I3" s="4">
+        <v>60</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="4">
+        <v>-58.26</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="4">
+        <v>18157.3</v>
+      </c>
+      <c r="I4" s="4">
+        <v>605</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="4">
+        <v>10</v>
+      </c>
+      <c r="L4" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="M4" s="4">
+        <v>10</v>
+      </c>
+      <c r="N4" s="4">
+        <v>25</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>44</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5">
+        <v>-58.26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>18157.3</v>
+      </c>
+      <c r="I5">
+        <v>605</v>
+      </c>
+      <c r="J5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>1.5</v>
+      </c>
+      <c r="M5">
+        <v>10</v>
+      </c>
+      <c r="N5">
+        <v>25</v>
+      </c>
+      <c r="O5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" t="s">
         <v>45</v>
       </c>
-      <c r="E3">
+      <c r="U5" t="s">
+        <v>54</v>
+      </c>
+      <c r="V5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6">
         <v>-58.26</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G6" t="s">
         <v>48</v>
       </c>
-      <c r="G3">
+      <c r="H6">
         <v>18157.3</v>
       </c>
-      <c r="H3">
+      <c r="I6">
+        <v>60.5</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>1.5</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+      <c r="N6">
+        <v>25</v>
+      </c>
+      <c r="O6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6" t="s">
+        <v>41</v>
+      </c>
+      <c r="S6" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" t="s">
+        <v>55</v>
+      </c>
+      <c r="V6" t="s">
         <v>60</v>
       </c>
-      <c r="I3" t="s">
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>-58.26</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7">
+        <v>18157.3</v>
+      </c>
+      <c r="I7">
+        <v>60.5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>1.5</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7">
+        <v>25</v>
+      </c>
+      <c r="O7" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S7" t="s">
+        <v>45</v>
+      </c>
+      <c r="U7" t="s">
+        <v>56</v>
+      </c>
+      <c r="V7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
         <v>52</v>
       </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>-58.26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8">
+        <v>18157.3</v>
+      </c>
+      <c r="I8">
+        <v>60.5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8">
+        <v>10</v>
+      </c>
+      <c r="L8">
+        <v>1.5</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
+      </c>
+      <c r="N8">
+        <v>25</v>
+      </c>
+      <c r="O8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R8" t="s">
+        <v>41</v>
+      </c>
+      <c r="S8" t="s">
+        <v>45</v>
+      </c>
+      <c r="U8" t="s">
+        <v>57</v>
+      </c>
+      <c r="V8" t="s">
         <v>58</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4">
-        <v>-58.26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4">
-        <v>18157.3</v>
-      </c>
-      <c r="H4">
-        <v>605</v>
-      </c>
-      <c r="I4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J4">
-        <v>10</v>
-      </c>
-      <c r="K4">
-        <v>1.5</v>
-      </c>
-      <c r="L4">
-        <v>10</v>
-      </c>
-      <c r="M4">
-        <v>25</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5">
-        <v>-58.26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5">
-        <v>18157.3</v>
-      </c>
-      <c r="H5">
-        <v>605</v>
-      </c>
-      <c r="I5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>1.5</v>
-      </c>
-      <c r="L5">
-        <v>10</v>
-      </c>
-      <c r="M5">
-        <v>25</v>
-      </c>
-      <c r="N5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P5" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>57</v>
-      </c>
-      <c r="R5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6">
-        <v>-58.26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6">
-        <v>18157.3</v>
-      </c>
-      <c r="H6">
-        <v>60.5</v>
-      </c>
-      <c r="I6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>1.5</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>25</v>
-      </c>
-      <c r="N6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O6" t="s">
-        <v>28</v>
-      </c>
-      <c r="P6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>57</v>
-      </c>
-      <c r="R6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7">
-        <v>-58.26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <v>18157.3</v>
-      </c>
-      <c r="H7">
-        <v>60.5</v>
-      </c>
-      <c r="I7" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>1.5</v>
-      </c>
-      <c r="L7">
-        <v>10</v>
-      </c>
-      <c r="M7">
-        <v>25</v>
-      </c>
-      <c r="N7" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" t="s">
-        <v>28</v>
-      </c>
-      <c r="P7" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>57</v>
-      </c>
-      <c r="R7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8">
-        <v>-58.26</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8">
-        <v>18157.3</v>
-      </c>
-      <c r="H8">
-        <v>60.5</v>
-      </c>
-      <c r="I8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
-      </c>
-      <c r="K8">
-        <v>1.5</v>
-      </c>
-      <c r="L8">
-        <v>10</v>
-      </c>
-      <c r="M8">
-        <v>25</v>
-      </c>
-      <c r="N8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O8" t="s">
-        <v>28</v>
-      </c>
-      <c r="P8" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>57</v>
-      </c>
-      <c r="R8" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:W8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898BBA13-6A69-4233-B716-3061FCC70632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58782B6-8C73-44A2-A19B-60BD69D01281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="case_matrix" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">case_matrix!$A$1:$W$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">case_matrix!$A$1:$AC$8</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="71">
   <si>
     <t>case_id</t>
   </si>
@@ -163,6 +163,12 @@
     <t>4..thermal_def_fix_mini_close_STT_all_time</t>
   </si>
   <si>
+    <t>C:\Users\Hide\Femap\research_model\03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5</t>
+  </si>
+  <si>
+    <t>results/femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5/los_angles.csv</t>
+  </si>
+  <si>
     <t>04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
   </si>
   <si>
@@ -172,6 +178,12 @@
     <t>MY</t>
   </si>
   <si>
+    <t>C:\Users\Hide\Femap\research_model\04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
+  </si>
+  <si>
+    <t>results/femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5/los_angles.csv</t>
+  </si>
+  <si>
     <t>05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
   </si>
   <si>
@@ -181,36 +193,58 @@
     <t>PX</t>
   </si>
   <si>
+    <t>C:\Users\Hide\Femap\research_model\05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
+  </si>
+  <si>
+    <t>results/femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5/los_angles.csv</t>
+  </si>
+  <si>
     <t>06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
   </si>
   <si>
     <t>STTLCT_HEAT</t>
   </si>
   <si>
-    <t>C:\Users\Hide\Femap\research_model\03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5</t>
-  </si>
-  <si>
-    <t>C:\Users\Hide\Femap\research_model\04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
+    <t>C:\Users\Hide\Femap\research_model\06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
+  </si>
+  <si>
+    <t>results/femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5/los_angles.csv</t>
+  </si>
+  <si>
+    <t>Opt_MX</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>C:\Users\Hide\Femap\research_model\05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
-  </si>
-  <si>
-    <t>C:\Users\Hide\Femap\research_model\06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
-  </si>
-  <si>
-    <t>C:\Users\Hide\repository\thermal-deformation-optcomm\results\femap_deformation\260702_1930_translation_rotation</t>
-  </si>
-  <si>
-    <t>C:\Users\Hide\repository\thermal-deformation-optcomm\results\femap_deformation\260702_1827_translation_rotation</t>
+    <t>Opt_MY</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>C:\Users\Hide\repository\thermal-deformation-optcomm\results\femap_deformation\260702_1103_translation_rotation</t>
-  </si>
-  <si>
-    <t>C:\Users\Hide\repository\thermal-deformation-optcomm\results\femap_deformation\260702_1023_translation_rotation</t>
+    <t>Opt_MZ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_PX</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_PY</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_PZ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>alodine1000</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Black</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>0p5</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -604,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="47.625" customWidth="1"/>
@@ -621,15 +655,21 @@
     <col min="12" max="12" width="15.625" customWidth="1"/>
     <col min="13" max="13" width="15.875" customWidth="1"/>
     <col min="14" max="17" width="16.375" customWidth="1"/>
-    <col min="18" max="18" width="35.625" customWidth="1"/>
-    <col min="19" max="19" width="42" customWidth="1"/>
-    <col min="20" max="20" width="30.75" customWidth="1"/>
-    <col min="21" max="21" width="21.5" customWidth="1"/>
-    <col min="22" max="22" width="24.5" customWidth="1"/>
-    <col min="23" max="23" width="11.875" customWidth="1"/>
+    <col min="18" max="18" width="12.375" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="12.625" customWidth="1"/>
+    <col min="21" max="21" width="12.25" customWidth="1"/>
+    <col min="22" max="22" width="11.375" customWidth="1"/>
+    <col min="23" max="23" width="12.625" customWidth="1"/>
+    <col min="24" max="24" width="35.625" customWidth="1"/>
+    <col min="25" max="25" width="42" customWidth="1"/>
+    <col min="26" max="26" width="30.75" customWidth="1"/>
+    <col min="27" max="27" width="21.5" customWidth="1"/>
+    <col min="28" max="28" width="24.5" customWidth="1"/>
+    <col min="29" max="29" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -682,25 +722,43 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
@@ -749,23 +807,23 @@
       <c r="Q2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:29" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>36</v>
       </c>
@@ -817,11 +875,11 @@
       <c r="Q3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="X3" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:29" s="4" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>42</v>
       </c>
@@ -873,11 +931,11 @@
       <c r="Q4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="X4" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -930,21 +988,39 @@
         <v>40</v>
       </c>
       <c r="R5" t="s">
+        <v>68</v>
+      </c>
+      <c r="S5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T5" t="s">
+        <v>70</v>
+      </c>
+      <c r="U5" t="s">
+        <v>68</v>
+      </c>
+      <c r="V5" t="s">
+        <v>68</v>
+      </c>
+      <c r="W5" t="s">
+        <v>68</v>
+      </c>
+      <c r="X5" t="s">
         <v>41</v>
       </c>
-      <c r="S5" t="s">
+      <c r="Y5" t="s">
         <v>45</v>
       </c>
-      <c r="U5" t="s">
-        <v>54</v>
-      </c>
-      <c r="V5" t="s">
-        <v>61</v>
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -956,13 +1032,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F6">
         <v>-58.26</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6">
         <v>18157.3</v>
@@ -995,21 +1071,39 @@
         <v>40</v>
       </c>
       <c r="R6" t="s">
+        <v>68</v>
+      </c>
+      <c r="S6" t="s">
+        <v>70</v>
+      </c>
+      <c r="T6" t="s">
+        <v>68</v>
+      </c>
+      <c r="U6" t="s">
+        <v>68</v>
+      </c>
+      <c r="V6" t="s">
+        <v>68</v>
+      </c>
+      <c r="W6" t="s">
+        <v>68</v>
+      </c>
+      <c r="X6" t="s">
         <v>41</v>
       </c>
-      <c r="S6" t="s">
+      <c r="Y6" t="s">
         <v>45</v>
       </c>
-      <c r="U6" t="s">
-        <v>55</v>
-      </c>
-      <c r="V6" t="s">
-        <v>60</v>
+      <c r="AA6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -1021,13 +1115,13 @@
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F7">
         <v>-58.26</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H7">
         <v>18157.3</v>
@@ -1060,21 +1154,39 @@
         <v>40</v>
       </c>
       <c r="R7" t="s">
+        <v>68</v>
+      </c>
+      <c r="S7" t="s">
+        <v>69</v>
+      </c>
+      <c r="T7" t="s">
+        <v>68</v>
+      </c>
+      <c r="U7" t="s">
+        <v>70</v>
+      </c>
+      <c r="V7" t="s">
+        <v>68</v>
+      </c>
+      <c r="W7" t="s">
+        <v>68</v>
+      </c>
+      <c r="X7" t="s">
         <v>41</v>
       </c>
-      <c r="S7" t="s">
+      <c r="Y7" t="s">
         <v>45</v>
       </c>
-      <c r="U7" t="s">
+      <c r="AA7" t="s">
         <v>56</v>
       </c>
-      <c r="V7" t="s">
-        <v>59</v>
+      <c r="AB7" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -1086,13 +1198,13 @@
         <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F8">
         <v>-58.26</v>
       </c>
       <c r="G8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H8">
         <v>18157.3</v>
@@ -1101,7 +1213,7 @@
         <v>60.5</v>
       </c>
       <c r="J8" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -1125,22 +1237,40 @@
         <v>40</v>
       </c>
       <c r="R8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S8" t="s">
+        <v>69</v>
+      </c>
+      <c r="T8" t="s">
+        <v>68</v>
+      </c>
+      <c r="U8" t="s">
+        <v>70</v>
+      </c>
+      <c r="V8" t="s">
+        <v>68</v>
+      </c>
+      <c r="W8" t="s">
+        <v>68</v>
+      </c>
+      <c r="X8" t="s">
         <v>41</v>
       </c>
-      <c r="S8" t="s">
+      <c r="Y8" t="s">
         <v>45</v>
       </c>
-      <c r="U8" t="s">
-        <v>57</v>
-      </c>
-      <c r="V8" t="s">
-        <v>58</v>
+      <c r="AA8" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AC8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58782B6-8C73-44A2-A19B-60BD69D01281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DF4BEF-2054-4326-B1EA-385726336FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="case_matrix" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">case_matrix!$A$1:$AC$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">case_matrix!$A$1:$AD$8</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="76">
   <si>
     <t>case_id</t>
   </si>
@@ -85,9 +85,6 @@
     <t>td_temperature_path</t>
   </si>
   <si>
-    <t>femap_result_path</t>
-  </si>
-  <si>
     <t>python_result_path</t>
   </si>
   <si>
@@ -169,81 +166,108 @@
     <t>results/femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5/los_angles.csv</t>
   </si>
   <si>
+    <t>LTAN06_800km_1213COLD_MY_SUN</t>
+  </si>
+  <si>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\Femap\research_model\04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
+  </si>
+  <si>
+    <t>results/femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5/los_angles.csv</t>
+  </si>
+  <si>
+    <t>LTAN06_800km_1213COLD_PX_SUN</t>
+  </si>
+  <si>
+    <t>PX</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\Femap\research_model\05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
+  </si>
+  <si>
+    <t>results/femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5/los_angles.csv</t>
+  </si>
+  <si>
+    <t>STTLCT_HEAT</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\Femap\research_model\06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
+  </si>
+  <si>
+    <t>results/femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5/los_angles.csv</t>
+  </si>
+  <si>
+    <t>Opt_MX</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_MY</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_MZ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_PX</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_PY</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_PZ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>alodine1000</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Black</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>0p5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>femap_result_stt_lct_path</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>femap_result_other_path</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>inputs/data_femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
-  </si>
-  <si>
-    <t>LTAN06_800km_1213COLD_MY_SUN</t>
-  </si>
-  <si>
-    <t>MY</t>
-  </si>
-  <si>
-    <t>C:\Users\Hide\Femap\research_model\04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
-  </si>
-  <si>
-    <t>results/femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5/los_angles.csv</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>inputs/data_femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
-  </si>
-  <si>
-    <t>LTAN06_800km_1213COLD_PX_SUN</t>
-  </si>
-  <si>
-    <t>PX</t>
-  </si>
-  <si>
-    <t>C:\Users\Hide\Femap\research_model\05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
-  </si>
-  <si>
-    <t>results/femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5/los_angles.csv</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>inputs/data_femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
-  </si>
-  <si>
-    <t>STTLCT_HEAT</t>
-  </si>
-  <si>
-    <t>C:\Users\Hide\Femap\research_model\06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
-  </si>
-  <si>
-    <t>results/femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5/los_angles.csv</t>
-  </si>
-  <si>
-    <t>Opt_MX</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_MY</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_MZ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_PX</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_PY</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_PZ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>alodine1000</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Black</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>0p5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>inputs/data_femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -638,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="47.625" customWidth="1"/>
@@ -663,13 +687,13 @@
     <col min="23" max="23" width="12.625" customWidth="1"/>
     <col min="24" max="24" width="35.625" customWidth="1"/>
     <col min="25" max="25" width="42" customWidth="1"/>
-    <col min="26" max="26" width="30.75" customWidth="1"/>
-    <col min="27" max="27" width="21.5" customWidth="1"/>
-    <col min="28" max="28" width="24.5" customWidth="1"/>
-    <col min="29" max="29" width="11.875" customWidth="1"/>
+    <col min="26" max="26" width="29.875" customWidth="1"/>
+    <col min="27" max="28" width="27" customWidth="1"/>
+    <col min="29" max="29" width="24.5" customWidth="1"/>
+    <col min="30" max="30" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -722,22 +746,22 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>17</v>
@@ -746,39 +770,42 @@
         <v>18</v>
       </c>
       <c r="Z1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AC1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F2" s="2">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" s="2">
         <v>16200</v>
@@ -787,7 +814,7 @@
         <v>600</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K2" s="2">
         <v>8</v>
@@ -799,51 +826,51 @@
         <v>12</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AC2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" s="4" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="F3" s="4">
         <v>-58.26</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3" s="4">
         <v>18157.3</v>
@@ -852,7 +879,7 @@
         <v>60</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K3" s="4">
         <v>0</v>
@@ -867,39 +894,39 @@
         <v>0</v>
       </c>
       <c r="O3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="Q3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" s="4" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="B4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="F4" s="4">
         <v>-58.26</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4" s="4">
         <v>18157.3</v>
@@ -908,7 +935,7 @@
         <v>605</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K4" s="4">
         <v>10</v>
@@ -923,39 +950,39 @@
         <v>25</v>
       </c>
       <c r="O4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="P4" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="Q4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="X4" s="4" t="s">
-        <v>41</v>
-      </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5">
         <v>-58.26</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5">
         <v>18157.3</v>
@@ -964,7 +991,7 @@
         <v>605</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -979,66 +1006,69 @@
         <v>25</v>
       </c>
       <c r="O5" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" t="s">
         <v>30</v>
       </c>
-      <c r="P5" t="s">
-        <v>31</v>
-      </c>
       <c r="Q5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R5" t="s">
+        <v>64</v>
+      </c>
+      <c r="S5" t="s">
+        <v>65</v>
+      </c>
+      <c r="T5" t="s">
+        <v>66</v>
+      </c>
+      <c r="U5" t="s">
+        <v>64</v>
+      </c>
+      <c r="V5" t="s">
+        <v>64</v>
+      </c>
+      <c r="W5" t="s">
+        <v>64</v>
+      </c>
+      <c r="X5" t="s">
         <v>40</v>
       </c>
-      <c r="R5" t="s">
-        <v>68</v>
-      </c>
-      <c r="S5" t="s">
+      <c r="Y5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" t="s">
         <v>69</v>
       </c>
-      <c r="T5" t="s">
+      <c r="AA5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>70</v>
       </c>
-      <c r="U5" t="s">
-        <v>68</v>
-      </c>
-      <c r="V5" t="s">
-        <v>68</v>
-      </c>
-      <c r="W5" t="s">
-        <v>68</v>
-      </c>
-      <c r="X5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB5" t="s">
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>49</v>
       </c>
       <c r="F6">
         <v>-58.26</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H6">
         <v>18157.3</v>
@@ -1047,7 +1077,7 @@
         <v>60.5</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -1062,66 +1092,69 @@
         <v>25</v>
       </c>
       <c r="O6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P6" t="s">
         <v>30</v>
       </c>
-      <c r="P6" t="s">
-        <v>31</v>
-      </c>
       <c r="Q6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R6" t="s">
+        <v>64</v>
+      </c>
+      <c r="S6" t="s">
+        <v>66</v>
+      </c>
+      <c r="T6" t="s">
+        <v>64</v>
+      </c>
+      <c r="U6" t="s">
+        <v>64</v>
+      </c>
+      <c r="V6" t="s">
+        <v>64</v>
+      </c>
+      <c r="W6" t="s">
+        <v>64</v>
+      </c>
+      <c r="X6" t="s">
         <v>40</v>
       </c>
-      <c r="R6" t="s">
-        <v>68</v>
-      </c>
-      <c r="S6" t="s">
-        <v>70</v>
-      </c>
-      <c r="T6" t="s">
-        <v>68</v>
-      </c>
-      <c r="U6" t="s">
-        <v>68</v>
-      </c>
-      <c r="V6" t="s">
-        <v>68</v>
-      </c>
-      <c r="W6" t="s">
-        <v>68</v>
-      </c>
-      <c r="X6" t="s">
-        <v>41</v>
-      </c>
       <c r="Y6" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>71</v>
       </c>
       <c r="AA6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
         <v>51</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>54</v>
       </c>
       <c r="F7">
         <v>-58.26</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H7">
         <v>18157.3</v>
@@ -1130,7 +1163,7 @@
         <v>60.5</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -1145,66 +1178,69 @@
         <v>25</v>
       </c>
       <c r="O7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" t="s">
         <v>30</v>
       </c>
-      <c r="P7" t="s">
-        <v>31</v>
-      </c>
       <c r="Q7" t="s">
+        <v>39</v>
+      </c>
+      <c r="R7" t="s">
+        <v>64</v>
+      </c>
+      <c r="S7" t="s">
+        <v>65</v>
+      </c>
+      <c r="T7" t="s">
+        <v>64</v>
+      </c>
+      <c r="U7" t="s">
+        <v>66</v>
+      </c>
+      <c r="V7" t="s">
+        <v>64</v>
+      </c>
+      <c r="W7" t="s">
+        <v>64</v>
+      </c>
+      <c r="X7" t="s">
         <v>40</v>
       </c>
-      <c r="R7" t="s">
-        <v>68</v>
-      </c>
-      <c r="S7" t="s">
-        <v>69</v>
-      </c>
-      <c r="T7" t="s">
-        <v>68</v>
-      </c>
-      <c r="U7" t="s">
-        <v>70</v>
-      </c>
-      <c r="V7" t="s">
-        <v>68</v>
-      </c>
-      <c r="W7" t="s">
-        <v>68</v>
-      </c>
-      <c r="X7" t="s">
-        <v>41</v>
-      </c>
       <c r="Y7" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>73</v>
       </c>
       <c r="AA7" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>25</v>
       </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F8">
         <v>-58.26</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H8">
         <v>18157.3</v>
@@ -1213,7 +1249,7 @@
         <v>60.5</v>
       </c>
       <c r="J8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -1228,47 +1264,50 @@
         <v>25</v>
       </c>
       <c r="O8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" t="s">
         <v>30</v>
       </c>
-      <c r="P8" t="s">
-        <v>31</v>
-      </c>
       <c r="Q8" t="s">
+        <v>39</v>
+      </c>
+      <c r="R8" t="s">
+        <v>64</v>
+      </c>
+      <c r="S8" t="s">
+        <v>65</v>
+      </c>
+      <c r="T8" t="s">
+        <v>64</v>
+      </c>
+      <c r="U8" t="s">
+        <v>66</v>
+      </c>
+      <c r="V8" t="s">
+        <v>64</v>
+      </c>
+      <c r="W8" t="s">
+        <v>64</v>
+      </c>
+      <c r="X8" t="s">
         <v>40</v>
       </c>
-      <c r="R8" t="s">
-        <v>68</v>
-      </c>
-      <c r="S8" t="s">
-        <v>69</v>
-      </c>
-      <c r="T8" t="s">
-        <v>68</v>
-      </c>
-      <c r="U8" t="s">
-        <v>70</v>
-      </c>
-      <c r="V8" t="s">
-        <v>68</v>
-      </c>
-      <c r="W8" t="s">
-        <v>68</v>
-      </c>
-      <c r="X8" t="s">
-        <v>41</v>
-      </c>
       <c r="Y8" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>75</v>
       </c>
       <c r="AA8" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>61</v>
+        <v>56</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AD8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DF4BEF-2054-4326-B1EA-385726336FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BE9F9D-6B5D-4DEA-A40A-D9446707F581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -154,120 +154,121 @@
     <t>ALL_HEAT</t>
   </si>
   <si>
+    <t>4..thermal_def_fix_mini_close_STT_all_time</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\Femap\research_model\03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5</t>
+  </si>
+  <si>
+    <t>results/femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5/los_angles.csv</t>
+  </si>
+  <si>
+    <t>LTAN06_800km_1213COLD_MY_SUN</t>
+  </si>
+  <si>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\Femap\research_model\04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
+  </si>
+  <si>
+    <t>results/femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5/los_angles.csv</t>
+  </si>
+  <si>
+    <t>LTAN06_800km_1213COLD_PX_SUN</t>
+  </si>
+  <si>
+    <t>PX</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\Femap\research_model\05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
+  </si>
+  <si>
+    <t>results/femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5/los_angles.csv</t>
+  </si>
+  <si>
+    <t>STTLCT_HEAT</t>
+  </si>
+  <si>
+    <t>C:\Users\Hide\Femap\research_model\06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
+  </si>
+  <si>
+    <t>results/femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5/los_angles.csv</t>
+  </si>
+  <si>
+    <t>Opt_MX</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_MY</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_MZ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_PX</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_PY</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Opt_PZ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>alodine1000</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Black</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>0p5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>femap_result_stt_lct_path</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>femap_result_other_path</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>inputs/data_femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>inputs/data_femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>inputs/data_femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>inputs/data_femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5</t>
-  </si>
-  <si>
-    <t>4..thermal_def_fix_mini_close_STT_all_time</t>
-  </si>
-  <si>
-    <t>C:\Users\Hide\Femap\research_model\03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5</t>
-  </si>
-  <si>
-    <t>results/femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5/los_angles.csv</t>
-  </si>
-  <si>
-    <t>LTAN06_800km_1213COLD_MY_SUN</t>
-  </si>
-  <si>
-    <t>MY</t>
-  </si>
-  <si>
-    <t>C:\Users\Hide\Femap\research_model\04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
-  </si>
-  <si>
-    <t>results/femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5/los_angles.csv</t>
-  </si>
-  <si>
-    <t>LTAN06_800km_1213COLD_PX_SUN</t>
-  </si>
-  <si>
-    <t>PX</t>
-  </si>
-  <si>
-    <t>C:\Users\Hide\Femap\research_model\05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
-  </si>
-  <si>
-    <t>results/femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5/los_angles.csv</t>
-  </si>
-  <si>
-    <t>STTLCT_HEAT</t>
-  </si>
-  <si>
-    <t>C:\Users\Hide\Femap\research_model\06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
-  </si>
-  <si>
-    <t>results/femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5/los_angles.csv</t>
-  </si>
-  <si>
-    <t>Opt_MX</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_MY</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_MZ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_PX</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_PY</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_PZ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>alodine1000</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Black</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>0p5</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>femap_result_stt_lct_path</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>femap_result_other_path</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>inputs/data_femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>inputs/data_femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>inputs/data_femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>inputs/data_femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -746,22 +747,22 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>17</v>
@@ -770,10 +771,10 @@
         <v>18</v>
       </c>
       <c r="Z1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="AB1" s="3" t="s">
         <v>19</v>
@@ -964,7 +965,7 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -1015,42 +1016,42 @@
         <v>39</v>
       </c>
       <c r="R5" t="s">
+        <v>63</v>
+      </c>
+      <c r="S5" t="s">
         <v>64</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>65</v>
       </c>
-      <c r="T5" t="s">
-        <v>66</v>
-      </c>
       <c r="U5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="V5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X5" t="s">
         <v>40</v>
       </c>
       <c r="Y5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA5" t="s">
         <v>44</v>
       </c>
-      <c r="Z5" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA5" t="s">
+      <c r="AC5" t="s">
         <v>45</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -1062,13 +1063,13 @@
         <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6">
         <v>-58.26</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H6">
         <v>18157.3</v>
@@ -1101,42 +1102,42 @@
         <v>39</v>
       </c>
       <c r="R6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="V6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X6" t="s">
         <v>40</v>
       </c>
       <c r="Y6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AA6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC6" t="s">
         <v>49</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
@@ -1148,13 +1149,13 @@
         <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7">
         <v>-58.26</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H7">
         <v>18157.3</v>
@@ -1187,42 +1188,42 @@
         <v>39</v>
       </c>
       <c r="R7" t="s">
+        <v>63</v>
+      </c>
+      <c r="S7" t="s">
         <v>64</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
+        <v>63</v>
+      </c>
+      <c r="U7" t="s">
         <v>65</v>
       </c>
-      <c r="T7" t="s">
-        <v>64</v>
-      </c>
-      <c r="U7" t="s">
-        <v>66</v>
-      </c>
       <c r="V7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X7" t="s">
         <v>40</v>
       </c>
       <c r="Y7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AA7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC7" t="s">
         <v>53</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -1234,13 +1235,13 @@
         <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F8">
         <v>-58.26</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8">
         <v>18157.3</v>
@@ -1249,7 +1250,7 @@
         <v>60.5</v>
       </c>
       <c r="J8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -1273,37 +1274,37 @@
         <v>39</v>
       </c>
       <c r="R8" t="s">
+        <v>63</v>
+      </c>
+      <c r="S8" t="s">
         <v>64</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
+        <v>63</v>
+      </c>
+      <c r="U8" t="s">
         <v>65</v>
       </c>
-      <c r="T8" t="s">
-        <v>64</v>
-      </c>
-      <c r="U8" t="s">
-        <v>66</v>
-      </c>
       <c r="V8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X8" t="s">
         <v>40</v>
       </c>
       <c r="Y8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AA8" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC8" t="s">
         <v>56</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BE9F9D-6B5D-4DEA-A40A-D9446707F581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17965B1A-479D-43FB-B9AA-A72EA71E1DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="case_matrix" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">case_matrix!$A$1:$AD$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">case_matrix!$A$1:$AC$8</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="75">
   <si>
     <t>case_id</t>
   </si>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t>constraint_set</t>
-  </si>
-  <si>
-    <t>td_temperature_path</t>
   </si>
   <si>
     <t>python_result_path</t>
@@ -663,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="47.625" customWidth="1"/>
@@ -689,12 +686,12 @@
     <col min="24" max="24" width="35.625" customWidth="1"/>
     <col min="25" max="25" width="42" customWidth="1"/>
     <col min="26" max="26" width="29.875" customWidth="1"/>
-    <col min="27" max="28" width="27" customWidth="1"/>
-    <col min="29" max="29" width="24.5" customWidth="1"/>
-    <col min="30" max="30" width="11.875" customWidth="1"/>
+    <col min="27" max="27" width="27" customWidth="1"/>
+    <col min="28" max="28" width="24.5" customWidth="1"/>
+    <col min="29" max="29" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -747,22 +744,22 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>17</v>
@@ -771,42 +768,39 @@
         <v>18</v>
       </c>
       <c r="Z1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AD1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F2" s="2">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2" s="2">
         <v>16200</v>
@@ -815,7 +809,7 @@
         <v>600</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K2" s="2">
         <v>8</v>
@@ -827,51 +821,51 @@
         <v>12</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>32</v>
       </c>
       <c r="AC2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AD2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:29" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="F3" s="4">
         <v>-58.26</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H3" s="4">
         <v>18157.3</v>
@@ -880,7 +874,7 @@
         <v>60</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K3" s="4">
         <v>0</v>
@@ -895,39 +889,39 @@
         <v>0</v>
       </c>
       <c r="O3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="Q3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="X3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:29" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="B4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="F4" s="4">
         <v>-58.26</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" s="4">
         <v>18157.3</v>
@@ -936,7 +930,7 @@
         <v>605</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4" s="4">
         <v>10</v>
@@ -951,39 +945,39 @@
         <v>25</v>
       </c>
       <c r="O4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="Q4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="X4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="X4" s="4" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>-58.26</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5">
         <v>18157.3</v>
@@ -992,7 +986,7 @@
         <v>605</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -1007,69 +1001,69 @@
         <v>25</v>
       </c>
       <c r="O5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" t="s">
         <v>29</v>
       </c>
-      <c r="P5" t="s">
-        <v>30</v>
-      </c>
       <c r="Q5" t="s">
+        <v>38</v>
+      </c>
+      <c r="R5" t="s">
+        <v>62</v>
+      </c>
+      <c r="S5" t="s">
+        <v>63</v>
+      </c>
+      <c r="T5" t="s">
+        <v>64</v>
+      </c>
+      <c r="U5" t="s">
+        <v>62</v>
+      </c>
+      <c r="V5" t="s">
+        <v>62</v>
+      </c>
+      <c r="W5" t="s">
+        <v>62</v>
+      </c>
+      <c r="X5" t="s">
         <v>39</v>
       </c>
-      <c r="R5" t="s">
-        <v>63</v>
-      </c>
-      <c r="S5" t="s">
-        <v>64</v>
-      </c>
-      <c r="T5" t="s">
-        <v>65</v>
-      </c>
-      <c r="U5" t="s">
-        <v>63</v>
-      </c>
-      <c r="V5" t="s">
-        <v>63</v>
-      </c>
-      <c r="W5" t="s">
-        <v>63</v>
-      </c>
-      <c r="X5" t="s">
-        <v>40</v>
-      </c>
       <c r="Y5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA5" t="s">
         <v>43</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AB5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>68</v>
       </c>
-      <c r="AA5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC5" t="s">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>46</v>
       </c>
       <c r="F6">
         <v>-58.26</v>
       </c>
       <c r="G6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H6">
         <v>18157.3</v>
@@ -1078,7 +1072,7 @@
         <v>60.5</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -1093,69 +1087,69 @@
         <v>25</v>
       </c>
       <c r="O6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" t="s">
         <v>29</v>
       </c>
-      <c r="P6" t="s">
-        <v>30</v>
-      </c>
       <c r="Q6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R6" t="s">
+        <v>62</v>
+      </c>
+      <c r="S6" t="s">
+        <v>64</v>
+      </c>
+      <c r="T6" t="s">
+        <v>62</v>
+      </c>
+      <c r="U6" t="s">
+        <v>62</v>
+      </c>
+      <c r="V6" t="s">
+        <v>62</v>
+      </c>
+      <c r="W6" t="s">
+        <v>62</v>
+      </c>
+      <c r="X6" t="s">
         <v>39</v>
       </c>
-      <c r="R6" t="s">
-        <v>63</v>
-      </c>
-      <c r="S6" t="s">
-        <v>65</v>
-      </c>
-      <c r="T6" t="s">
-        <v>63</v>
-      </c>
-      <c r="U6" t="s">
-        <v>63</v>
-      </c>
-      <c r="V6" t="s">
-        <v>63</v>
-      </c>
-      <c r="W6" t="s">
-        <v>63</v>
-      </c>
-      <c r="X6" t="s">
-        <v>40</v>
-      </c>
       <c r="Y6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
         <v>70</v>
       </c>
-      <c r="AA6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC6" t="s">
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>50</v>
       </c>
       <c r="F7">
         <v>-58.26</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H7">
         <v>18157.3</v>
@@ -1164,7 +1158,7 @@
         <v>60.5</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -1179,69 +1173,69 @@
         <v>25</v>
       </c>
       <c r="O7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" t="s">
         <v>29</v>
       </c>
-      <c r="P7" t="s">
-        <v>30</v>
-      </c>
       <c r="Q7" t="s">
+        <v>38</v>
+      </c>
+      <c r="R7" t="s">
+        <v>62</v>
+      </c>
+      <c r="S7" t="s">
+        <v>63</v>
+      </c>
+      <c r="T7" t="s">
+        <v>62</v>
+      </c>
+      <c r="U7" t="s">
+        <v>64</v>
+      </c>
+      <c r="V7" t="s">
+        <v>62</v>
+      </c>
+      <c r="W7" t="s">
+        <v>62</v>
+      </c>
+      <c r="X7" t="s">
         <v>39</v>
       </c>
-      <c r="R7" t="s">
-        <v>63</v>
-      </c>
-      <c r="S7" t="s">
-        <v>64</v>
-      </c>
-      <c r="T7" t="s">
-        <v>63</v>
-      </c>
-      <c r="U7" t="s">
-        <v>65</v>
-      </c>
-      <c r="V7" t="s">
-        <v>63</v>
-      </c>
-      <c r="W7" t="s">
-        <v>63</v>
-      </c>
-      <c r="X7" t="s">
-        <v>40</v>
-      </c>
       <c r="Y7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
         <v>72</v>
       </c>
-      <c r="AA7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>73</v>
-      </c>
       <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8">
         <v>-58.26</v>
       </c>
       <c r="G8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H8">
         <v>18157.3</v>
@@ -1250,7 +1244,7 @@
         <v>60.5</v>
       </c>
       <c r="J8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -1265,50 +1259,50 @@
         <v>25</v>
       </c>
       <c r="O8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" t="s">
         <v>29</v>
       </c>
-      <c r="P8" t="s">
-        <v>30</v>
-      </c>
       <c r="Q8" t="s">
+        <v>38</v>
+      </c>
+      <c r="R8" t="s">
+        <v>62</v>
+      </c>
+      <c r="S8" t="s">
+        <v>63</v>
+      </c>
+      <c r="T8" t="s">
+        <v>62</v>
+      </c>
+      <c r="U8" t="s">
+        <v>64</v>
+      </c>
+      <c r="V8" t="s">
+        <v>62</v>
+      </c>
+      <c r="W8" t="s">
+        <v>62</v>
+      </c>
+      <c r="X8" t="s">
         <v>39</v>
       </c>
-      <c r="R8" t="s">
-        <v>63</v>
-      </c>
-      <c r="S8" t="s">
-        <v>64</v>
-      </c>
-      <c r="T8" t="s">
-        <v>63</v>
-      </c>
-      <c r="U8" t="s">
-        <v>65</v>
-      </c>
-      <c r="V8" t="s">
-        <v>63</v>
-      </c>
-      <c r="W8" t="s">
-        <v>63</v>
-      </c>
-      <c r="X8" t="s">
-        <v>40</v>
-      </c>
       <c r="Y8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AA8" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB8" t="s">
         <v>55</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AC8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17965B1A-479D-43FB-B9AA-A72EA71E1DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9917C0-144F-4D5A-91C7-6337FE75C3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="case_matrix" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="93">
   <si>
     <t>case_id</t>
   </si>
@@ -266,6 +266,70 @@
   </si>
   <si>
     <t>03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>07_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5_delta_t_60s</t>
+  </si>
+  <si>
+    <t>08_LTAN06_800km_1213COLD_PY_ALL_HEAT_PY_0p5</t>
+  </si>
+  <si>
+    <t>09_LTAN06_800km_1213COLD_MX_ALL_HEAT_MX_0p5</t>
+  </si>
+  <si>
+    <t>10_LTAN06_800km_HOT_MY_ALL_HEAT_MY_0p5</t>
+  </si>
+  <si>
+    <t>11_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_Black</t>
+  </si>
+  <si>
+    <t>12_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_alodine</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>15_LTAN06_800km_1213COLD_MY_STTLCT_HEAT_MY_0p5</t>
+  </si>
+  <si>
+    <t>LTAN06_800km_1213COLD_PY_SUN</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LTAN06_800km_HOT_MY_SUN</t>
+  </si>
+  <si>
+    <t>LTAN06_800km_1213COLD_MX_SUN</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MZ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>PY</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MX</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MY</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13_LTAN06_800km_1213COLD_MY_STTLCT_PROP_HEAT_MY_0p5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>STTLCT_PROP_HEAT</t>
+  </si>
+  <si>
+    <t>14_LTAN06_800km_1213COLD_MY_STTLCT_PCDU_HEAT_MY_0p5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>STTLCT_PCDU_HEAT</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -660,33 +724,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="47.625" customWidth="1"/>
+    <col min="1" max="1" width="53.5" customWidth="1"/>
     <col min="2" max="2" width="16.5" customWidth="1"/>
     <col min="3" max="3" width="17.75" customWidth="1"/>
     <col min="4" max="4" width="30.5" customWidth="1"/>
-    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="5" max="5" width="32.5" customWidth="1"/>
     <col min="6" max="6" width="19.25" customWidth="1"/>
-    <col min="7" max="7" width="14.875" customWidth="1"/>
-    <col min="8" max="8" width="21.625" customWidth="1"/>
+    <col min="7" max="8" width="21.625" customWidth="1"/>
     <col min="9" max="9" width="17.75" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="10" max="10" width="18.875" customWidth="1"/>
     <col min="11" max="11" width="14.375" customWidth="1"/>
     <col min="12" max="12" width="15.625" customWidth="1"/>
     <col min="13" max="13" width="15.875" customWidth="1"/>
     <col min="14" max="17" width="16.375" customWidth="1"/>
-    <col min="18" max="18" width="12.375" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="20" max="20" width="12.625" customWidth="1"/>
-    <col min="21" max="21" width="12.25" customWidth="1"/>
-    <col min="22" max="22" width="11.375" customWidth="1"/>
-    <col min="23" max="23" width="12.625" customWidth="1"/>
-    <col min="24" max="24" width="35.625" customWidth="1"/>
+    <col min="18" max="18" width="20.625" customWidth="1"/>
+    <col min="19" max="19" width="12.375" customWidth="1"/>
+    <col min="20" max="20" width="13" customWidth="1"/>
+    <col min="21" max="21" width="12.625" customWidth="1"/>
+    <col min="22" max="22" width="12.25" customWidth="1"/>
+    <col min="23" max="23" width="11.375" customWidth="1"/>
+    <col min="24" max="24" width="12.625" customWidth="1"/>
     <col min="25" max="25" width="42" customWidth="1"/>
     <col min="26" max="26" width="29.875" customWidth="1"/>
-    <col min="27" max="27" width="27" customWidth="1"/>
+    <col min="27" max="27" width="56.25" customWidth="1"/>
     <col min="28" max="28" width="24.5" customWidth="1"/>
     <col min="29" max="29" width="11.875" customWidth="1"/>
   </cols>
@@ -744,25 +807,25 @@
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>18</v>
@@ -829,7 +892,7 @@
       <c r="Q2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="Y2" s="2" t="s">
@@ -897,7 +960,7 @@
       <c r="Q3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -953,7 +1016,7 @@
       <c r="Q4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="R4" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -961,8 +1024,8 @@
       <c r="A5" t="s">
         <v>74</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
+      <c r="B5" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -1010,17 +1073,17 @@
         <v>38</v>
       </c>
       <c r="R5" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="S5" t="s">
+        <v>62</v>
+      </c>
+      <c r="T5" t="s">
         <v>63</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>64</v>
       </c>
-      <c r="U5" t="s">
-        <v>62</v>
-      </c>
       <c r="V5" t="s">
         <v>62</v>
       </c>
@@ -1028,7 +1091,7 @@
         <v>62</v>
       </c>
       <c r="X5" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="Y5" t="s">
         <v>42</v>
@@ -1096,14 +1159,14 @@
         <v>38</v>
       </c>
       <c r="R6" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="S6" t="s">
+        <v>62</v>
+      </c>
+      <c r="T6" t="s">
         <v>64</v>
       </c>
-      <c r="T6" t="s">
-        <v>62</v>
-      </c>
       <c r="U6" t="s">
         <v>62</v>
       </c>
@@ -1114,7 +1177,7 @@
         <v>62</v>
       </c>
       <c r="X6" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="Y6" t="s">
         <v>42</v>
@@ -1182,25 +1245,25 @@
         <v>38</v>
       </c>
       <c r="R7" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="S7" t="s">
+        <v>62</v>
+      </c>
+      <c r="T7" t="s">
         <v>63</v>
       </c>
-      <c r="T7" t="s">
-        <v>62</v>
-      </c>
       <c r="U7" t="s">
+        <v>62</v>
+      </c>
+      <c r="V7" t="s">
         <v>64</v>
       </c>
-      <c r="V7" t="s">
-        <v>62</v>
-      </c>
       <c r="W7" t="s">
         <v>62</v>
       </c>
       <c r="X7" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="Y7" t="s">
         <v>42</v>
@@ -1253,10 +1316,10 @@
         <v>1.5</v>
       </c>
       <c r="M8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="s">
         <v>28</v>
@@ -1268,25 +1331,25 @@
         <v>38</v>
       </c>
       <c r="R8" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="S8" t="s">
+        <v>62</v>
+      </c>
+      <c r="T8" t="s">
         <v>63</v>
       </c>
-      <c r="T8" t="s">
-        <v>62</v>
-      </c>
       <c r="U8" t="s">
+        <v>62</v>
+      </c>
+      <c r="V8" t="s">
         <v>64</v>
       </c>
-      <c r="V8" t="s">
-        <v>62</v>
-      </c>
       <c r="W8" t="s">
         <v>62</v>
       </c>
       <c r="X8" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="Y8" t="s">
         <v>42</v>
@@ -1299,6 +1362,699 @@
       </c>
       <c r="AB8" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9">
+        <v>-58.26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9">
+        <v>18157.3</v>
+      </c>
+      <c r="I9">
+        <v>60.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+      <c r="L9">
+        <v>1.5</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+      <c r="N9">
+        <v>25</v>
+      </c>
+      <c r="O9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S9" t="s">
+        <v>62</v>
+      </c>
+      <c r="T9" t="s">
+        <v>63</v>
+      </c>
+      <c r="U9" t="s">
+        <v>64</v>
+      </c>
+      <c r="V9" t="s">
+        <v>62</v>
+      </c>
+      <c r="W9" t="s">
+        <v>62</v>
+      </c>
+      <c r="X9" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10">
+        <v>-58.26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10">
+        <v>18157.3</v>
+      </c>
+      <c r="I10">
+        <v>60.5</v>
+      </c>
+      <c r="J10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10">
+        <v>10</v>
+      </c>
+      <c r="L10">
+        <v>1.5</v>
+      </c>
+      <c r="M10">
+        <v>10</v>
+      </c>
+      <c r="N10">
+        <v>25</v>
+      </c>
+      <c r="O10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>38</v>
+      </c>
+      <c r="R10" t="s">
+        <v>39</v>
+      </c>
+      <c r="S10" t="s">
+        <v>62</v>
+      </c>
+      <c r="T10" t="s">
+        <v>63</v>
+      </c>
+      <c r="U10" t="s">
+        <v>62</v>
+      </c>
+      <c r="V10" t="s">
+        <v>62</v>
+      </c>
+      <c r="W10" t="s">
+        <v>64</v>
+      </c>
+      <c r="X10" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11">
+        <v>-58.26</v>
+      </c>
+      <c r="G11" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11">
+        <v>18157.3</v>
+      </c>
+      <c r="I11">
+        <v>60.5</v>
+      </c>
+      <c r="J11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>1.5</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>25</v>
+      </c>
+      <c r="O11" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>38</v>
+      </c>
+      <c r="R11" t="s">
+        <v>39</v>
+      </c>
+      <c r="S11" t="s">
+        <v>64</v>
+      </c>
+      <c r="T11" t="s">
+        <v>63</v>
+      </c>
+      <c r="U11" t="s">
+        <v>62</v>
+      </c>
+      <c r="V11" t="s">
+        <v>62</v>
+      </c>
+      <c r="W11" t="s">
+        <v>62</v>
+      </c>
+      <c r="X11" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12">
+        <v>-81.36</v>
+      </c>
+      <c r="G12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12">
+        <v>18157.3</v>
+      </c>
+      <c r="I12">
+        <v>60.5</v>
+      </c>
+      <c r="J12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
+      <c r="L12">
+        <v>1.5</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="N12">
+        <v>25</v>
+      </c>
+      <c r="O12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>38</v>
+      </c>
+      <c r="R12" t="s">
+        <v>39</v>
+      </c>
+      <c r="S12" t="s">
+        <v>62</v>
+      </c>
+      <c r="T12" t="s">
+        <v>64</v>
+      </c>
+      <c r="U12" t="s">
+        <v>62</v>
+      </c>
+      <c r="V12" t="s">
+        <v>62</v>
+      </c>
+      <c r="W12" t="s">
+        <v>62</v>
+      </c>
+      <c r="X12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13">
+        <v>-58.26</v>
+      </c>
+      <c r="G13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13">
+        <v>18157.3</v>
+      </c>
+      <c r="I13">
+        <v>60.5</v>
+      </c>
+      <c r="J13" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>1.5</v>
+      </c>
+      <c r="M13">
+        <v>10</v>
+      </c>
+      <c r="N13">
+        <v>25</v>
+      </c>
+      <c r="O13" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S13" t="s">
+        <v>62</v>
+      </c>
+      <c r="T13" t="s">
+        <v>63</v>
+      </c>
+      <c r="U13" t="s">
+        <v>62</v>
+      </c>
+      <c r="V13" t="s">
+        <v>62</v>
+      </c>
+      <c r="W13" t="s">
+        <v>62</v>
+      </c>
+      <c r="X13" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14">
+        <v>-58.26</v>
+      </c>
+      <c r="G14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14">
+        <v>18157.3</v>
+      </c>
+      <c r="I14">
+        <v>60.5</v>
+      </c>
+      <c r="J14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14">
+        <v>10</v>
+      </c>
+      <c r="L14">
+        <v>1.5</v>
+      </c>
+      <c r="M14">
+        <v>10</v>
+      </c>
+      <c r="N14">
+        <v>25</v>
+      </c>
+      <c r="O14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>38</v>
+      </c>
+      <c r="R14" t="s">
+        <v>39</v>
+      </c>
+      <c r="S14" t="s">
+        <v>62</v>
+      </c>
+      <c r="T14" t="s">
+        <v>62</v>
+      </c>
+      <c r="U14" t="s">
+        <v>62</v>
+      </c>
+      <c r="V14" t="s">
+        <v>62</v>
+      </c>
+      <c r="W14" t="s">
+        <v>62</v>
+      </c>
+      <c r="X14" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15">
+        <v>-58.26</v>
+      </c>
+      <c r="G15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15">
+        <v>18157.3</v>
+      </c>
+      <c r="I15">
+        <v>60.5</v>
+      </c>
+      <c r="J15" t="s">
+        <v>90</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15">
+        <v>1.5</v>
+      </c>
+      <c r="M15">
+        <v>10</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R15" t="s">
+        <v>39</v>
+      </c>
+      <c r="S15" t="s">
+        <v>62</v>
+      </c>
+      <c r="T15" t="s">
+        <v>64</v>
+      </c>
+      <c r="U15" t="s">
+        <v>62</v>
+      </c>
+      <c r="V15" t="s">
+        <v>62</v>
+      </c>
+      <c r="W15" t="s">
+        <v>62</v>
+      </c>
+      <c r="X15" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16">
+        <v>-58.26</v>
+      </c>
+      <c r="G16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16">
+        <v>18157.3</v>
+      </c>
+      <c r="I16">
+        <v>60.5</v>
+      </c>
+      <c r="J16" t="s">
+        <v>92</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16">
+        <v>1.5</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>25</v>
+      </c>
+      <c r="O16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>38</v>
+      </c>
+      <c r="R16" t="s">
+        <v>39</v>
+      </c>
+      <c r="S16" t="s">
+        <v>62</v>
+      </c>
+      <c r="T16" t="s">
+        <v>64</v>
+      </c>
+      <c r="U16" t="s">
+        <v>62</v>
+      </c>
+      <c r="V16" t="s">
+        <v>62</v>
+      </c>
+      <c r="W16" t="s">
+        <v>62</v>
+      </c>
+      <c r="X16" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17">
+        <v>-58.26</v>
+      </c>
+      <c r="G17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17">
+        <v>18157.3</v>
+      </c>
+      <c r="I17">
+        <v>60.5</v>
+      </c>
+      <c r="J17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17">
+        <v>10</v>
+      </c>
+      <c r="L17">
+        <v>1.5</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>38</v>
+      </c>
+      <c r="R17" t="s">
+        <v>39</v>
+      </c>
+      <c r="S17" t="s">
+        <v>62</v>
+      </c>
+      <c r="T17" t="s">
+        <v>64</v>
+      </c>
+      <c r="U17" t="s">
+        <v>62</v>
+      </c>
+      <c r="V17" t="s">
+        <v>62</v>
+      </c>
+      <c r="W17" t="s">
+        <v>62</v>
+      </c>
+      <c r="X17" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hidek\repository\thermal-deformation-optcomm\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9917C0-144F-4D5A-91C7-6337FE75C3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="case_matrix" sheetId="1" r:id="rId1"/>
@@ -725,36 +725,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC17"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="53.5" customWidth="1"/>
-    <col min="2" max="2" width="16.5" customWidth="1"/>
-    <col min="3" max="3" width="17.75" customWidth="1"/>
-    <col min="4" max="4" width="30.5" customWidth="1"/>
-    <col min="5" max="5" width="32.5" customWidth="1"/>
-    <col min="6" max="6" width="19.25" customWidth="1"/>
-    <col min="7" max="8" width="21.625" customWidth="1"/>
-    <col min="9" max="9" width="17.75" customWidth="1"/>
-    <col min="10" max="10" width="18.875" customWidth="1"/>
-    <col min="11" max="11" width="14.375" customWidth="1"/>
-    <col min="12" max="12" width="15.625" customWidth="1"/>
-    <col min="13" max="13" width="15.875" customWidth="1"/>
-    <col min="14" max="17" width="16.375" customWidth="1"/>
-    <col min="18" max="18" width="20.625" customWidth="1"/>
-    <col min="19" max="19" width="12.375" customWidth="1"/>
+    <col min="1" max="1" width="53.453125" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.7265625" customWidth="1"/>
+    <col min="4" max="4" width="30.453125" customWidth="1"/>
+    <col min="5" max="5" width="32.453125" customWidth="1"/>
+    <col min="6" max="6" width="19.26953125" customWidth="1"/>
+    <col min="7" max="8" width="21.6328125" customWidth="1"/>
+    <col min="9" max="9" width="17.7265625" customWidth="1"/>
+    <col min="10" max="10" width="18.90625" customWidth="1"/>
+    <col min="11" max="11" width="14.36328125" customWidth="1"/>
+    <col min="12" max="12" width="15.6328125" customWidth="1"/>
+    <col min="13" max="13" width="15.90625" customWidth="1"/>
+    <col min="14" max="17" width="16.36328125" customWidth="1"/>
+    <col min="18" max="18" width="20.6328125" customWidth="1"/>
+    <col min="19" max="19" width="12.36328125" customWidth="1"/>
     <col min="20" max="20" width="13" customWidth="1"/>
-    <col min="21" max="21" width="12.625" customWidth="1"/>
-    <col min="22" max="22" width="12.25" customWidth="1"/>
-    <col min="23" max="23" width="11.375" customWidth="1"/>
-    <col min="24" max="24" width="12.625" customWidth="1"/>
+    <col min="21" max="21" width="12.6328125" customWidth="1"/>
+    <col min="22" max="22" width="12.26953125" customWidth="1"/>
+    <col min="23" max="23" width="11.36328125" customWidth="1"/>
+    <col min="24" max="24" width="12.6328125" customWidth="1"/>
     <col min="25" max="25" width="42" customWidth="1"/>
-    <col min="26" max="26" width="29.875" customWidth="1"/>
-    <col min="27" max="27" width="56.25" customWidth="1"/>
-    <col min="28" max="28" width="24.5" customWidth="1"/>
-    <col min="29" max="29" width="11.875" customWidth="1"/>
+    <col min="26" max="26" width="29.90625" customWidth="1"/>
+    <col min="27" max="27" width="56.26953125" customWidth="1"/>
+    <col min="28" max="28" width="24.453125" customWidth="1"/>
+    <col min="29" max="29" width="11.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -843,7 +843,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -908,7 +908,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="4" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:29" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>34</v>
       </c>
@@ -964,7 +964,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="4" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:29" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>68</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>70</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>72</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>75</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>76</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>77</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>79</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>80</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>91</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>81</v>
       </c>

--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -5,25 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hidek\repository\thermal-deformation-optcomm\cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9917C0-144F-4D5A-91C7-6337FE75C3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24E839B-CB05-4020-BB2B-F0D5BA78AEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="case_matrix" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">case_matrix!$A$1:$AC$8</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="103">
   <si>
     <t>case_id</t>
   </si>
@@ -79,9 +76,33 @@
     <t>prop_location</t>
   </si>
   <si>
+    <t>Opt_MX</t>
+  </si>
+  <si>
+    <t>Opt_MY</t>
+  </si>
+  <si>
+    <t>Opt_MZ</t>
+  </si>
+  <si>
+    <t>Opt_PX</t>
+  </si>
+  <si>
+    <t>Opt_PY</t>
+  </si>
+  <si>
+    <t>Opt_PZ</t>
+  </si>
+  <si>
     <t>constraint_set</t>
   </si>
   <si>
+    <t>femap_result_stt_lct_path</t>
+  </si>
+  <si>
+    <t>femap_result_other_path</t>
+  </si>
+  <si>
     <t>python_result_path</t>
   </si>
   <si>
@@ -151,193 +172,170 @@
     <t>ALL_HEAT</t>
   </si>
   <si>
+    <t>03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5</t>
+  </si>
+  <si>
+    <t>alodine1000</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>0p5</t>
+  </si>
+  <si>
     <t>4..thermal_def_fix_mini_close_STT_all_time</t>
   </si>
   <si>
+    <t>inputs/data_femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx</t>
+  </si>
+  <si>
     <t>C:\Users\Hide\Femap\research_model\03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5</t>
   </si>
   <si>
     <t>results/femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5/los_angles.csv</t>
   </si>
   <si>
+    <t>04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
+  </si>
+  <si>
     <t>LTAN06_800km_1213COLD_MY_SUN</t>
   </si>
   <si>
     <t>MY</t>
   </si>
   <si>
+    <t>inputs/data_femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx</t>
+  </si>
+  <si>
     <t>C:\Users\Hide\Femap\research_model\04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
   </si>
   <si>
     <t>results/femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5/los_angles.csv</t>
   </si>
   <si>
+    <t>05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
+  </si>
+  <si>
     <t>LTAN06_800km_1213COLD_PX_SUN</t>
   </si>
   <si>
     <t>PX</t>
   </si>
   <si>
+    <t>inputs/data_femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx</t>
+  </si>
+  <si>
     <t>C:\Users\Hide\Femap\research_model\05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
   </si>
   <si>
     <t>results/femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5/los_angles.csv</t>
   </si>
   <si>
+    <t>06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
+  </si>
+  <si>
     <t>STTLCT_HEAT</t>
   </si>
   <si>
+    <t>inputs/data_femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx</t>
+  </si>
+  <si>
     <t>C:\Users\Hide\Femap\research_model\06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
   </si>
   <si>
     <t>results/femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5/los_angles.csv</t>
   </si>
   <si>
-    <t>Opt_MX</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_MY</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_MZ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_PX</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_PY</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Opt_PZ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>alodine1000</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Black</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>0p5</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>femap_result_stt_lct_path</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>femap_result_other_path</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>inputs/data_femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>inputs/data_femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>inputs/data_femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>inputs/data_femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>07_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5_delta_t_60s</t>
   </si>
   <si>
     <t>08_LTAN06_800km_1213COLD_PY_ALL_HEAT_PY_0p5</t>
   </si>
   <si>
+    <t>LTAN06_800km_1213COLD_PY_SUN</t>
+  </si>
+  <si>
+    <t>PY</t>
+  </si>
+  <si>
     <t>09_LTAN06_800km_1213COLD_MX_ALL_HEAT_MX_0p5</t>
   </si>
   <si>
+    <t>LTAN06_800km_1213COLD_MX_SUN</t>
+  </si>
+  <si>
+    <t>MX</t>
+  </si>
+  <si>
     <t>10_LTAN06_800km_HOT_MY_ALL_HEAT_MY_0p5</t>
   </si>
   <si>
+    <t>LTAN06_800km_HOT_MY_SUN</t>
+  </si>
+  <si>
     <t>11_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_Black</t>
   </si>
   <si>
     <t>12_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_alodine</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13_LTAN06_800km_1213COLD_MY_STTLCT_PROP_HEAT_MY_0p5</t>
+  </si>
+  <si>
+    <t>STTLCT_PROP_HEAT</t>
+  </si>
+  <si>
+    <t>14_LTAN06_800km_1213COLD_MY_STTLCT_PCDU_HEAT_MY_0p5</t>
+  </si>
+  <si>
+    <t>STTLCT_PCDU_HEAT</t>
   </si>
   <si>
     <t>15_LTAN06_800km_1213COLD_MY_STTLCT_HEAT_MY_0p5</t>
   </si>
   <si>
-    <t>LTAN06_800km_1213COLD_PY_SUN</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>LTAN06_800km_HOT_MY_SUN</t>
-  </si>
-  <si>
-    <t>LTAN06_800km_1213COLD_MX_SUN</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MZ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>PY</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MX</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MY</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>13_LTAN06_800km_1213COLD_MY_STTLCT_PROP_HEAT_MY_0p5</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>STTLCT_PROP_HEAT</t>
-  </si>
-  <si>
-    <t>14_LTAN06_800km_1213COLD_MY_STTLCT_PCDU_HEAT_MY_0p5</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>STTLCT_PCDU_HEAT</t>
-    <phoneticPr fontId="2"/>
+    <t>16_LTAN06_800km_1213COLD_PY_STTLCT_HEAT_PY_0p5</t>
+  </si>
+  <si>
+    <t>PY sun: STTLCT only (pair with 08 ALL). For b DC vs internal heat.</t>
+  </si>
+  <si>
+    <t>17_LTAN06_800km_1213COLD_MX_STTLCT_HEAT_MX_0p5</t>
+  </si>
+  <si>
+    <t>MX sun: STTLCT only (pair with 09 ALL).</t>
+  </si>
+  <si>
+    <t>18_LTAN06_800km_1213COLD_PY_STTLCT_PROP_HEAT_PY_0p5</t>
+  </si>
+  <si>
+    <t>PY sun heat screen: PROP on sun-face panel (pair with 16/19/08).</t>
+  </si>
+  <si>
+    <t>19_LTAN06_800km_1213COLD_PY_STTLCT_PCDU_HEAT_PY_0p5</t>
+  </si>
+  <si>
+    <t>PY sun heat screen: PCDU on opposite (MY) panel.</t>
+  </si>
+  <si>
+    <t>20_LTAN06_800km_1213COLD_PX_STTLCT_PROP_HEAT_PX_0p5</t>
+  </si>
+  <si>
+    <t>PX sun heat screen: PROP only (completes PX like MY 13).</t>
+  </si>
+  <si>
+    <t>21_LTAN06_800km_1213COLD_PX_STTLCT_PCDU_HEAT_PX_0p5</t>
+  </si>
+  <si>
+    <t>PX sun heat screen: PCDU only (completes PX like MY 14).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,58 +344,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -412,16 +371,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -724,323 +675,299 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC17"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AC23"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="53.453125" customWidth="1"/>
-    <col min="2" max="2" width="16.453125" customWidth="1"/>
-    <col min="3" max="3" width="17.7265625" customWidth="1"/>
-    <col min="4" max="4" width="30.453125" customWidth="1"/>
-    <col min="5" max="5" width="32.453125" customWidth="1"/>
-    <col min="6" max="6" width="19.26953125" customWidth="1"/>
-    <col min="7" max="8" width="21.6328125" customWidth="1"/>
-    <col min="9" max="9" width="17.7265625" customWidth="1"/>
-    <col min="10" max="10" width="18.90625" customWidth="1"/>
-    <col min="11" max="11" width="14.36328125" customWidth="1"/>
-    <col min="12" max="12" width="15.6328125" customWidth="1"/>
-    <col min="13" max="13" width="15.90625" customWidth="1"/>
-    <col min="14" max="17" width="16.36328125" customWidth="1"/>
-    <col min="18" max="18" width="20.6328125" customWidth="1"/>
-    <col min="19" max="19" width="12.36328125" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
-    <col min="21" max="21" width="12.6328125" customWidth="1"/>
-    <col min="22" max="22" width="12.26953125" customWidth="1"/>
-    <col min="23" max="23" width="11.36328125" customWidth="1"/>
-    <col min="24" max="24" width="12.6328125" customWidth="1"/>
-    <col min="25" max="25" width="42" customWidth="1"/>
-    <col min="26" max="26" width="29.90625" customWidth="1"/>
-    <col min="27" max="27" width="56.26953125" customWidth="1"/>
-    <col min="28" max="28" width="24.453125" customWidth="1"/>
-    <col min="29" max="29" width="11.90625" customWidth="1"/>
+    <col min="1" max="1" width="55.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2">
+        <v>16200</v>
+      </c>
+      <c r="I2">
+        <v>600</v>
+      </c>
+      <c r="J2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2">
+        <v>8</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>12</v>
+      </c>
+      <c r="O2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3">
+        <v>-58.26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3">
+        <v>18157.3</v>
+      </c>
+      <c r="I3">
         <v>60</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>20</v>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="2" t="s">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4">
+        <v>-58.26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4">
+        <v>18157.3</v>
+      </c>
+      <c r="I4">
+        <v>605</v>
+      </c>
+      <c r="J4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4">
+        <v>1.5</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+      <c r="N4">
         <v>25</v>
       </c>
-      <c r="F2" s="2">
-        <v>30</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="2">
-        <v>16200</v>
-      </c>
-      <c r="I2" s="2">
-        <v>600</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="2">
-        <v>8</v>
-      </c>
-      <c r="L2" s="2">
-        <v>2</v>
-      </c>
-      <c r="N2" s="2">
-        <v>12</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" s="2" t="s">
+      <c r="O4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
         <v>31</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="D5" t="s">
         <v>32</v>
       </c>
-      <c r="AC2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="4">
-        <v>-58.26</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="4">
-        <v>18157.3</v>
-      </c>
-      <c r="I3" s="4">
-        <v>60</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="4">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4">
-        <v>0</v>
-      </c>
-      <c r="M3" s="4">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="4">
-        <v>-58.26</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="4">
-        <v>18157.3</v>
-      </c>
-      <c r="I4" s="4">
-        <v>605</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="4">
-        <v>10</v>
-      </c>
-      <c r="L4" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="M4" s="4">
-        <v>10</v>
-      </c>
-      <c r="N4" s="4">
-        <v>25</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F5">
         <v>-58.26</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H5">
         <v>18157.3</v>
@@ -1049,7 +976,7 @@
         <v>605</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -1064,69 +991,69 @@
         <v>25</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S5" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="T5" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="U5" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="V5" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="W5" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X5" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Y5" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="Z5" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="AB5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F6">
         <v>-58.26</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H6">
         <v>18157.3</v>
@@ -1135,7 +1062,7 @@
         <v>60.5</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -1150,69 +1077,69 @@
         <v>25</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T6" t="s">
+        <v>53</v>
+      </c>
+      <c r="U6" t="s">
+        <v>51</v>
+      </c>
+      <c r="V6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W6" t="s">
+        <v>51</v>
+      </c>
+      <c r="X6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA6" t="s">
         <v>62</v>
       </c>
-      <c r="T6" t="s">
+      <c r="AB6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
         <v>64</v>
       </c>
-      <c r="U6" t="s">
-        <v>62</v>
-      </c>
-      <c r="V6" t="s">
-        <v>62</v>
-      </c>
-      <c r="W6" t="s">
-        <v>62</v>
-      </c>
-      <c r="X6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>70</v>
-      </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F7">
         <v>-58.26</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="H7">
         <v>18157.3</v>
@@ -1221,7 +1148,7 @@
         <v>60.5</v>
       </c>
       <c r="J7" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -1236,69 +1163,69 @@
         <v>25</v>
       </c>
       <c r="O7" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P7" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q7" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R7" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="T7" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="U7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="V7" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="W7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Y7" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="Z7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="AA7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="AB7" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F8">
         <v>-58.26</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="H8">
         <v>18157.3</v>
@@ -1307,7 +1234,7 @@
         <v>60.5</v>
       </c>
       <c r="J8" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -1322,69 +1249,69 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P8" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R8" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S8" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="T8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="U8" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="V8" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="W8" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X8" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Y8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="Z8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA8" t="s">
         <v>73</v>
       </c>
-      <c r="AA8" t="s">
-        <v>54</v>
-      </c>
       <c r="AB8" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F9">
         <v>-58.26</v>
       </c>
       <c r="G9" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="H9">
         <v>18157.3</v>
@@ -1393,7 +1320,7 @@
         <v>60.5</v>
       </c>
       <c r="J9" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K9">
         <v>10</v>
@@ -1408,60 +1335,60 @@
         <v>25</v>
       </c>
       <c r="O9" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P9" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S9" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="T9" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="U9" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="V9" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="W9" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X9" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Y9" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F10">
         <v>-58.26</v>
       </c>
       <c r="G10" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H10">
         <v>18157.3</v>
@@ -1470,7 +1397,7 @@
         <v>60.5</v>
       </c>
       <c r="J10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K10">
         <v>10</v>
@@ -1485,60 +1412,60 @@
         <v>25</v>
       </c>
       <c r="O10" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P10" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R10" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S10" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="T10" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="U10" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="V10" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="W10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="X10" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Y10" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F11">
         <v>-58.26</v>
       </c>
       <c r="G11" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H11">
         <v>18157.3</v>
@@ -1547,7 +1474,7 @@
         <v>60.5</v>
       </c>
       <c r="J11" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -1562,51 +1489,51 @@
         <v>25</v>
       </c>
       <c r="O11" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P11" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q11" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R11" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S11" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="T11" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="U11" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="V11" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="W11" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X11" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Y11" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
         <v>83</v>
@@ -1615,7 +1542,7 @@
         <v>-81.36</v>
       </c>
       <c r="G12" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H12">
         <v>18157.3</v>
@@ -1624,7 +1551,7 @@
         <v>60.5</v>
       </c>
       <c r="J12" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K12">
         <v>10</v>
@@ -1639,60 +1566,60 @@
         <v>25</v>
       </c>
       <c r="O12" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P12" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q12" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R12" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S12" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="T12" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="U12" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="V12" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="W12" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X12" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Y12" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F13">
         <v>-58.26</v>
       </c>
       <c r="G13" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H13">
         <v>18157.3</v>
@@ -1701,7 +1628,7 @@
         <v>60.5</v>
       </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -1716,60 +1643,60 @@
         <v>25</v>
       </c>
       <c r="O13" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P13" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q13" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R13" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S13" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="T13" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="U13" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="V13" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="W13" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X13" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Y13" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F14">
         <v>-58.26</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H14">
         <v>18157.3</v>
@@ -1778,7 +1705,7 @@
         <v>60.5</v>
       </c>
       <c r="J14" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K14">
         <v>10</v>
@@ -1793,60 +1720,60 @@
         <v>25</v>
       </c>
       <c r="O14" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P14" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q14" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R14" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S14" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="T14" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="U14" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="V14" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="W14" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X14" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Y14" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F15">
         <v>-58.26</v>
       </c>
       <c r="G15" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H15">
         <v>18157.3</v>
@@ -1855,7 +1782,7 @@
         <v>60.5</v>
       </c>
       <c r="J15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K15">
         <v>10</v>
@@ -1870,60 +1797,60 @@
         <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P15" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q15" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R15" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S15" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="T15" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="U15" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="V15" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="W15" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X15" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Y15" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F16">
         <v>-58.26</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H16">
         <v>18157.3</v>
@@ -1932,7 +1859,7 @@
         <v>60.5</v>
       </c>
       <c r="J16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -1947,60 +1874,60 @@
         <v>25</v>
       </c>
       <c r="O16" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P16" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q16" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R16" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S16" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="T16" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="U16" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="V16" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="W16" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X16" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Y16" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F17">
         <v>-58.26</v>
       </c>
       <c r="G17" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H17">
         <v>18157.3</v>
@@ -2009,7 +1936,7 @@
         <v>60.5</v>
       </c>
       <c r="J17" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="K17">
         <v>10</v>
@@ -2024,43 +1951,521 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P17" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q17" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R17" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S17" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="T17" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="U17" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="V17" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="W17" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X17" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Y17" t="s">
-        <v>42</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18">
+        <v>-58.26</v>
+      </c>
+      <c r="G18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18">
+        <v>18157.3</v>
+      </c>
+      <c r="I18">
+        <v>60.5</v>
+      </c>
+      <c r="J18" t="s">
+        <v>71</v>
+      </c>
+      <c r="K18">
+        <v>10</v>
+      </c>
+      <c r="L18">
+        <v>1.5</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>36</v>
+      </c>
+      <c r="P18" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>46</v>
+      </c>
+      <c r="R18" t="s">
+        <v>47</v>
+      </c>
+      <c r="S18" t="s">
+        <v>51</v>
+      </c>
+      <c r="T18" t="s">
+        <v>52</v>
+      </c>
+      <c r="U18" t="s">
+        <v>51</v>
+      </c>
+      <c r="V18" t="s">
+        <v>51</v>
+      </c>
+      <c r="W18" t="s">
+        <v>53</v>
+      </c>
+      <c r="X18" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19">
+        <v>-58.26</v>
+      </c>
+      <c r="G19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19">
+        <v>18157.3</v>
+      </c>
+      <c r="I19">
+        <v>60.5</v>
+      </c>
+      <c r="J19" t="s">
+        <v>71</v>
+      </c>
+      <c r="K19">
+        <v>10</v>
+      </c>
+      <c r="L19">
+        <v>1.5</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P19" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>46</v>
+      </c>
+      <c r="R19" t="s">
+        <v>47</v>
+      </c>
+      <c r="S19" t="s">
+        <v>53</v>
+      </c>
+      <c r="T19" t="s">
+        <v>52</v>
+      </c>
+      <c r="U19" t="s">
+        <v>51</v>
+      </c>
+      <c r="V19" t="s">
+        <v>51</v>
+      </c>
+      <c r="W19" t="s">
+        <v>51</v>
+      </c>
+      <c r="X19" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20">
+        <v>-58.26</v>
+      </c>
+      <c r="G20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20">
+        <v>18157.3</v>
+      </c>
+      <c r="I20">
+        <v>60.5</v>
+      </c>
+      <c r="J20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K20">
+        <v>10</v>
+      </c>
+      <c r="L20">
+        <v>1.5</v>
+      </c>
+      <c r="M20">
+        <v>10</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>36</v>
+      </c>
+      <c r="P20" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R20" t="s">
+        <v>47</v>
+      </c>
+      <c r="S20" t="s">
+        <v>51</v>
+      </c>
+      <c r="T20" t="s">
+        <v>52</v>
+      </c>
+      <c r="U20" t="s">
+        <v>51</v>
+      </c>
+      <c r="V20" t="s">
+        <v>51</v>
+      </c>
+      <c r="W20" t="s">
+        <v>53</v>
+      </c>
+      <c r="X20" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21">
+        <v>-58.26</v>
+      </c>
+      <c r="G21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21">
+        <v>18157.3</v>
+      </c>
+      <c r="I21">
+        <v>60.5</v>
+      </c>
+      <c r="J21" t="s">
+        <v>89</v>
+      </c>
+      <c r="K21">
+        <v>10</v>
+      </c>
+      <c r="L21">
+        <v>1.5</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>25</v>
+      </c>
+      <c r="O21" t="s">
+        <v>36</v>
+      </c>
+      <c r="P21" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>46</v>
+      </c>
+      <c r="R21" t="s">
+        <v>47</v>
+      </c>
+      <c r="S21" t="s">
+        <v>51</v>
+      </c>
+      <c r="T21" t="s">
+        <v>52</v>
+      </c>
+      <c r="U21" t="s">
+        <v>51</v>
+      </c>
+      <c r="V21" t="s">
+        <v>51</v>
+      </c>
+      <c r="W21" t="s">
+        <v>53</v>
+      </c>
+      <c r="X21" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22">
+        <v>-58.26</v>
+      </c>
+      <c r="G22" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22">
+        <v>18157.3</v>
+      </c>
+      <c r="I22">
+        <v>60.5</v>
+      </c>
+      <c r="J22" t="s">
+        <v>87</v>
+      </c>
+      <c r="K22">
+        <v>10</v>
+      </c>
+      <c r="L22">
+        <v>1.5</v>
+      </c>
+      <c r="M22">
+        <v>10</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>36</v>
+      </c>
+      <c r="P22" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R22" t="s">
+        <v>47</v>
+      </c>
+      <c r="S22" t="s">
+        <v>51</v>
+      </c>
+      <c r="T22" t="s">
+        <v>52</v>
+      </c>
+      <c r="U22" t="s">
+        <v>51</v>
+      </c>
+      <c r="V22" t="s">
+        <v>53</v>
+      </c>
+      <c r="W22" t="s">
+        <v>51</v>
+      </c>
+      <c r="X22" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23">
+        <v>-58.26</v>
+      </c>
+      <c r="G23" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23">
+        <v>18157.3</v>
+      </c>
+      <c r="I23">
+        <v>60.5</v>
+      </c>
+      <c r="J23" t="s">
+        <v>89</v>
+      </c>
+      <c r="K23">
+        <v>10</v>
+      </c>
+      <c r="L23">
+        <v>1.5</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>25</v>
+      </c>
+      <c r="O23" t="s">
+        <v>36</v>
+      </c>
+      <c r="P23" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R23" t="s">
+        <v>47</v>
+      </c>
+      <c r="S23" t="s">
+        <v>51</v>
+      </c>
+      <c r="T23" t="s">
+        <v>52</v>
+      </c>
+      <c r="U23" t="s">
+        <v>51</v>
+      </c>
+      <c r="V23" t="s">
+        <v>53</v>
+      </c>
+      <c r="W23" t="s">
+        <v>51</v>
+      </c>
+      <c r="X23" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24E839B-CB05-4020-BB2B-F0D5BA78AEB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77DEBD2-D69A-43A0-9EC4-05ABB86BF741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="104">
   <si>
     <t>case_id</t>
   </si>
@@ -329,6 +329,10 @@
   </si>
   <si>
     <t>PX sun heat screen: PCDU only (completes PX like MY 14).</t>
+  </si>
+  <si>
+    <t>4..thermal_def_fix_mini_close_STT_all_time</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -2458,7 +2462,7 @@
         <v>51</v>
       </c>
       <c r="Y23" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="AC23" t="s">
         <v>102</v>

--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="case_matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="case_matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -18,18 +19,14 @@
   <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <sz val="6"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,15 +45,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -419,154 +425,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
-  <cols>
-    <col width="53.75" customWidth="1" min="1" max="1"/>
-  </cols>
+  <dimension ref="A1:Z26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>case_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>case_group</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>use_for_model</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>spacecraft_model</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>orbit_case</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>beta_angle_deg</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sun_direction_body</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>duration_s</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>sample_interval_s</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>power_mode</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>lct_heat_w</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>stt_heat_w</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prop_heat_w</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>pcdu_heat_w</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>lct_location</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>stt_location</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>pcdu_location</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>prop_location</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Opt_MX</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Opt_MY</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Opt_MZ</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Opt_PX</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Opt_PY</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Opt_PZ</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>constraint_set</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>femap_result_stt_lct_path</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>femap_result_other_path</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>python_result_path</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -649,6 +637,14 @@
           <t>PY_MZside</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -727,6 +723,14 @@
           <t>PY_MZside</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -840,21 +844,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>inputs/data_femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>C:\Users\Hide\Femap\research_model\03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>results/femap_deformation/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5/los_angles.csv</t>
-        </is>
-      </c>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -968,21 +958,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>inputs/data_femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>C:\Users\Hide\Femap\research_model\04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>results/femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5/los_angles.csv</t>
-        </is>
-      </c>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1096,21 +1072,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>inputs/data_femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5.xlsx</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>C:\Users\Hide\Femap\research_model\05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>results/femap_deformation/05_LTAN06_800km_1213COLD_PX_ALL_HEAT_PX_0p5/los_angles.csv</t>
-        </is>
-      </c>
+      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1224,21 +1186,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>inputs/data_femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5.xlsx</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>C:\Users\Hide\Femap\research_model\06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>results/femap_deformation/06_LTAN06_800km_1213COLD_PX_STTLCT_HEAT_PX_0p5/los_angles.csv</t>
-        </is>
-      </c>
+      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1352,6 +1300,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1465,6 +1414,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1578,6 +1528,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1691,6 +1642,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1804,6 +1756,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1917,6 +1870,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2030,6 +1984,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2143,6 +2098,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2256,6 +2212,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2369,7 +2326,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>PY sun: STTLCT only (pair with 08 ALL). For b DC vs internal heat.</t>
         </is>
@@ -2487,7 +2444,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>MX sun: STTLCT only (pair with 09 ALL).</t>
         </is>
@@ -2605,7 +2562,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>PY sun heat screen: PROP on sun-face panel (pair with 16/19/08).</t>
         </is>
@@ -2723,7 +2680,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>PY sun heat screen: PCDU on opposite (MY) panel.</t>
         </is>
@@ -2841,7 +2798,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>PX sun heat screen: PROP only (completes PX like MY 13).</t>
         </is>
@@ -2959,7 +2916,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>PX sun heat screen: PCDU only (completes PX like MY 14).</t>
         </is>
@@ -3077,7 +3034,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>OpenTD create spike: clone case04, INT_HEAT_PROP=12.5 (continuous W). Not for model.</t>
         </is>
@@ -3195,7 +3152,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>A: MX heat screen +PROP (pair with 17/09; MY analog=13)</t>
         </is>
@@ -3313,7 +3270,7 @@
           <t>4..thermal_def_fix_mini_close_STT_all_time</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>A: MX heat screen +PCDU (pair with 17/09; MY analog=14)</t>
         </is>
@@ -3345,6 +3302,7 @@
           <t>LTAN18_693km_SENTINEL1_MY_SUN</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>MY</t>
@@ -3429,21 +3387,6 @@
         </is>
       </c>
       <c r="Z26" t="inlineStr">
-        <is>
-          <t>inputs/data_femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5.xlsx</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>C:\Users\Hide\Femap\research_model\04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>results/femap_deformation/04_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_0p5/los_angles.csv</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
         <is>
           <t>E: Sentinel-1 nominal orbit (693km LTAN18) MY ALL; compare to case04 COLD800</t>
         </is>

--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hidek\repository\thermal-deformation-optcomm\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89967AF9-A923-44CA-8267-93DD1BCC8ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014401D4-789E-48C3-996D-03278337B6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -664,7 +664,11 @@
   <dimension ref="A1:Z26"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="55.7265625" customWidth="1"/>
+    <col min="1" max="1" width="46.08984375" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="16.90625" customWidth="1"/>
+    <col min="5" max="5" width="21.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">

--- a/cases/case_matrix.xlsx
+++ b/cases/case_matrix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hidek\repository\thermal-deformation-optcomm\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014401D4-789E-48C3-996D-03278337B6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61B0C43-E299-455E-91F9-C2BB328A27ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -668,7 +668,7 @@
     <col min="2" max="2" width="10.453125" customWidth="1"/>
     <col min="3" max="3" width="13.54296875" customWidth="1"/>
     <col min="4" max="4" width="16.90625" customWidth="1"/>
-    <col min="5" max="5" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="26.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
